--- a/datasehat.xlsx
+++ b/datasehat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\sehatselenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49794CD-562E-4BF2-9637-81B339593148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67581154-1DAF-409B-A964-F35A14710D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -25,23 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nama</t>
   </si>
   <si>
-    <t>siti syarifah</t>
-  </si>
-  <si>
-    <t>moch mahfud</t>
-  </si>
-  <si>
-    <t>turnaesih</t>
-  </si>
-  <si>
-    <t>parwati</t>
-  </si>
-  <si>
     <t>sistol</t>
   </si>
   <si>
@@ -60,47 +48,26 @@
     <t>GDS</t>
   </si>
   <si>
-    <t>SITI KULSUM</t>
-  </si>
-  <si>
-    <t>AGUS MAHMUD</t>
-  </si>
-  <si>
-    <t>KARMANAH</t>
-  </si>
-  <si>
-    <t>YAKUB BASTAMAN</t>
-  </si>
-  <si>
-    <t>HOTDIANA SINAMBELA</t>
-  </si>
-  <si>
-    <t>WARSAN, TN</t>
-  </si>
-  <si>
     <t>HESRON SAUT MARULI</t>
   </si>
   <si>
-    <t>FAULINA</t>
-  </si>
-  <si>
-    <t>81,4</t>
-  </si>
-  <si>
-    <t>ROSANNA BR BANGUN</t>
-  </si>
-  <si>
-    <t>LALA RUCHMANA</t>
-  </si>
-  <si>
-    <t>APRILDAYANTI</t>
+    <t>CINDY AYU LESTARI</t>
+  </si>
+  <si>
+    <t>ROHIM</t>
+  </si>
+  <si>
+    <t>KASURIP MULYO SLAMET</t>
+  </si>
+  <si>
+    <t>66,9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +92,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -216,40 +190,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -262,18 +222,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,417 +567,236 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" s="1">
+        <v>114</v>
+      </c>
+      <c r="C2" s="2">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2">
+        <v>145</v>
+      </c>
+      <c r="E2" s="2">
+        <v>42</v>
+      </c>
+      <c r="F2" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2">
+        <v>78</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3" s="1">
+        <v>120</v>
+      </c>
+      <c r="C3" s="2">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2">
+        <v>154</v>
+      </c>
+      <c r="E3" s="2">
+        <v>66</v>
+      </c>
+      <c r="F3" s="2">
+        <v>95</v>
+      </c>
+      <c r="G3" s="2">
+        <v>87</v>
+      </c>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4" s="3">
+        <v>120</v>
+      </c>
+      <c r="C4" s="4">
+        <v>70</v>
+      </c>
+      <c r="D4" s="4">
+        <v>170</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4">
+        <v>84</v>
+      </c>
+      <c r="G4" s="4">
+        <v>86</v>
+      </c>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>164</v>
-      </c>
-      <c r="C2" s="2">
-        <v>90</v>
-      </c>
-      <c r="D2" s="2">
-        <v>155</v>
-      </c>
-      <c r="E2" s="2">
-        <v>75</v>
-      </c>
-      <c r="F2" s="2">
-        <v>88</v>
-      </c>
-      <c r="G2" s="2">
-        <v>94</v>
-      </c>
-      <c r="H2" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3">
-        <v>137</v>
-      </c>
-      <c r="C3" s="4">
-        <v>92</v>
-      </c>
-      <c r="D3" s="4">
-        <v>158</v>
-      </c>
-      <c r="E3" s="4">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82</v>
-      </c>
-      <c r="G3" s="4">
-        <v>97</v>
-      </c>
-      <c r="H3" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
-        <v>114</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B5" s="3">
+        <v>120</v>
+      </c>
+      <c r="C5" s="4">
         <v>80</v>
       </c>
-      <c r="D4" s="4">
-        <v>155</v>
-      </c>
-      <c r="E4" s="4">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4">
-        <v>67</v>
-      </c>
-      <c r="G4" s="4">
-        <v>78</v>
-      </c>
-      <c r="H4" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <v>152</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="D5" s="4">
+        <v>174</v>
+      </c>
+      <c r="E5" s="4">
+        <v>74</v>
+      </c>
+      <c r="F5" s="4">
+        <v>84</v>
+      </c>
+      <c r="G5" s="4">
         <v>98</v>
       </c>
-      <c r="D5" s="4">
-        <v>155</v>
-      </c>
-      <c r="E5" s="4">
-        <v>61</v>
-      </c>
-      <c r="F5" s="4">
-        <v>67</v>
-      </c>
-      <c r="G5" s="4">
-        <v>114</v>
-      </c>
-      <c r="H5" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1">
-        <v>181</v>
-      </c>
-      <c r="C6" s="2">
-        <v>93</v>
-      </c>
-      <c r="D6" s="2">
-        <v>150</v>
-      </c>
-      <c r="E6" s="2">
-        <v>51</v>
-      </c>
-      <c r="F6" s="2">
-        <v>82</v>
-      </c>
-      <c r="G6" s="2">
-        <v>114</v>
-      </c>
-      <c r="H6" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3">
-        <v>177</v>
-      </c>
-      <c r="C7" s="4">
-        <v>103</v>
-      </c>
-      <c r="D7" s="4">
-        <v>160</v>
-      </c>
-      <c r="E7" s="4">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4">
-        <v>84</v>
-      </c>
-      <c r="G7" s="4">
-        <v>84</v>
-      </c>
-      <c r="H7" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
-        <v>198</v>
-      </c>
-      <c r="C8" s="4">
-        <v>109</v>
-      </c>
-      <c r="D8" s="4">
-        <v>150</v>
-      </c>
-      <c r="E8" s="4">
-        <v>59</v>
-      </c>
-      <c r="F8" s="4">
-        <v>86</v>
-      </c>
-      <c r="G8" s="4">
-        <v>85</v>
-      </c>
-      <c r="H8" s="11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3">
-        <v>109</v>
-      </c>
-      <c r="C9" s="4">
-        <v>75</v>
-      </c>
-      <c r="D9" s="4">
-        <v>160</v>
-      </c>
-      <c r="E9" s="4">
-        <v>88</v>
-      </c>
-      <c r="F9" s="4">
-        <v>84</v>
-      </c>
-      <c r="G9" s="4">
-        <v>75</v>
-      </c>
-      <c r="H9" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="7">
-        <v>110</v>
-      </c>
-      <c r="C10" s="8">
-        <v>70</v>
-      </c>
-      <c r="D10" s="8">
-        <v>150</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="8">
-        <v>90</v>
-      </c>
-      <c r="G10" s="8">
-        <v>79</v>
-      </c>
-      <c r="H10" s="11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="9">
-        <v>120</v>
-      </c>
-      <c r="C11" s="10">
-        <v>80</v>
-      </c>
-      <c r="D11" s="10">
-        <v>164</v>
-      </c>
-      <c r="E11" s="10">
-        <v>60</v>
-      </c>
-      <c r="F11" s="10">
-        <v>90</v>
-      </c>
-      <c r="G11" s="10">
-        <v>105</v>
-      </c>
-      <c r="H11" s="11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="9">
-        <v>130</v>
-      </c>
-      <c r="C12" s="10">
-        <v>90</v>
-      </c>
-      <c r="D12" s="10">
-        <v>162</v>
-      </c>
-      <c r="E12" s="10">
-        <v>65</v>
-      </c>
-      <c r="F12" s="10">
-        <v>82</v>
-      </c>
-      <c r="G12" s="10">
-        <v>84</v>
-      </c>
-      <c r="H12" s="11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="9">
-        <v>114</v>
-      </c>
-      <c r="C13" s="10">
-        <v>77</v>
-      </c>
-      <c r="D13" s="10">
-        <v>145</v>
-      </c>
-      <c r="E13" s="10">
-        <v>42</v>
-      </c>
-      <c r="F13" s="10">
-        <v>70</v>
-      </c>
-      <c r="G13" s="10">
-        <v>78</v>
-      </c>
-      <c r="H13" s="12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="7">
-        <v>120</v>
-      </c>
-      <c r="C14" s="8">
-        <v>70</v>
-      </c>
-      <c r="D14" s="8">
-        <v>150</v>
-      </c>
-      <c r="E14" s="8">
-        <v>55</v>
-      </c>
-      <c r="F14" s="8">
-        <v>78</v>
-      </c>
-      <c r="G14" s="8">
-        <v>85</v>
-      </c>
-      <c r="H14" s="11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="9">
-        <v>90</v>
-      </c>
-      <c r="C15" s="10">
-        <v>60</v>
-      </c>
-      <c r="D15" s="10">
-        <v>157</v>
-      </c>
-      <c r="E15" s="10">
-        <v>73</v>
-      </c>
-      <c r="F15" s="10">
-        <v>85</v>
-      </c>
-      <c r="G15" s="10">
-        <v>89</v>
-      </c>
-      <c r="H15" s="12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="9">
-        <v>110</v>
-      </c>
-      <c r="C16" s="10">
-        <v>70</v>
-      </c>
-      <c r="D16" s="10">
-        <v>150</v>
-      </c>
-      <c r="E16" s="10">
-        <v>55</v>
-      </c>
-      <c r="F16" s="10">
-        <v>78</v>
-      </c>
-      <c r="G16" s="10">
-        <v>89</v>
-      </c>
-      <c r="H16" s="11">
-        <v>14</v>
-      </c>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasehat.xlsx
+++ b/datasehat.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\sehatselenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67581154-1DAF-409B-A964-F35A14710D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8CD937-6DE7-44CD-817A-2209422D71B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
+    <workbookView xWindow="8604" yWindow="1884" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="daftar" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>nama</t>
   </si>
@@ -48,26 +49,95 @@
     <t>GDS</t>
   </si>
   <si>
-    <t>HESRON SAUT MARULI</t>
-  </si>
-  <si>
-    <t>CINDY AYU LESTARI</t>
-  </si>
-  <si>
-    <t>ROHIM</t>
-  </si>
-  <si>
-    <t>KASURIP MULYO SLAMET</t>
-  </si>
-  <si>
-    <t>66,9</t>
+    <t>nik</t>
+  </si>
+  <si>
+    <t>BALQIST AN NISA NURDINI</t>
+  </si>
+  <si>
+    <t>tanggal_lahir</t>
+  </si>
+  <si>
+    <t>2003-03-11</t>
+  </si>
+  <si>
+    <t>Perempuan</t>
+  </si>
+  <si>
+    <t>3671015103030006</t>
+  </si>
+  <si>
+    <t>jenis_kelamin</t>
+  </si>
+  <si>
+    <t>nomor_whatsapp</t>
+  </si>
+  <si>
+    <t>Pegawai Swasta</t>
+  </si>
+  <si>
+    <t>pekerjaan</t>
+  </si>
+  <si>
+    <t>provinsi</t>
+  </si>
+  <si>
+    <t>Banten</t>
+  </si>
+  <si>
+    <t>kota</t>
+  </si>
+  <si>
+    <t>Kota Tangerang</t>
+  </si>
+  <si>
+    <t>kecamatan</t>
+  </si>
+  <si>
+    <t>Tangerang</t>
+  </si>
+  <si>
+    <t>kelurahan</t>
+  </si>
+  <si>
+    <t>Tanah Tinggi</t>
+  </si>
+  <si>
+    <t>alamat</t>
+  </si>
+  <si>
+    <t>RONGGUR HALOMOAN LUBIS</t>
+  </si>
+  <si>
+    <t>NURYANDI</t>
+  </si>
+  <si>
+    <t>AHMAD BUKHORI</t>
+  </si>
+  <si>
+    <t>SYAM RAGIL RAHARJO</t>
+  </si>
+  <si>
+    <t>SURYA CAHYA DININGRAT</t>
+  </si>
+  <si>
+    <t>DIAN NOVITA SARI</t>
+  </si>
+  <si>
+    <t>USNIAWATI</t>
+  </si>
+  <si>
+    <t>RINI SUTARTI</t>
+  </si>
+  <si>
+    <t>ZIDNA RAHAYU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,17 +158,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="8"/>
+      <color rgb="FF343A40"/>
+      <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -116,47 +179,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -204,11 +237,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -216,35 +288,41 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,246 +638,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE509DE-262C-4991-9047-33EC594D87BB}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1">
-        <v>114</v>
-      </c>
-      <c r="C2" s="2">
-        <v>77</v>
-      </c>
-      <c r="D2" s="2">
-        <v>145</v>
-      </c>
-      <c r="E2" s="2">
-        <v>42</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="9">
+        <v>110</v>
+      </c>
+      <c r="C2" s="10">
         <v>70</v>
       </c>
-      <c r="G2" s="2">
-        <v>78</v>
-      </c>
-      <c r="H2" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="D2" s="10">
+        <v>156</v>
+      </c>
+      <c r="E2" s="10">
+        <v>92</v>
+      </c>
+      <c r="F2" s="10">
+        <v>80</v>
+      </c>
+      <c r="G2" s="10">
+        <v>82</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="11">
+        <v>130</v>
+      </c>
+      <c r="C3" s="12">
+        <v>90</v>
+      </c>
+      <c r="D3" s="12">
+        <v>156</v>
+      </c>
+      <c r="E3" s="12">
+        <v>70</v>
+      </c>
+      <c r="F3" s="12">
+        <v>86</v>
+      </c>
+      <c r="G3" s="12">
+        <v>82</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="11">
+        <v>100</v>
+      </c>
+      <c r="C4" s="12">
+        <v>70</v>
+      </c>
+      <c r="D4" s="12">
+        <v>158</v>
+      </c>
+      <c r="E4" s="12">
+        <v>55</v>
+      </c>
+      <c r="F4" s="12">
+        <v>86</v>
+      </c>
+      <c r="G4" s="12">
+        <v>83</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="11">
+        <v>100</v>
+      </c>
+      <c r="C5" s="12">
+        <v>60</v>
+      </c>
+      <c r="D5" s="12">
+        <v>157</v>
+      </c>
+      <c r="E5" s="12">
+        <v>81</v>
+      </c>
+      <c r="F5" s="12">
+        <v>82</v>
+      </c>
+      <c r="G5" s="12">
+        <v>84</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="11">
         <v>120</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C6" s="12">
         <v>80</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D6" s="12">
+        <v>156</v>
+      </c>
+      <c r="E6" s="12">
+        <v>58</v>
+      </c>
+      <c r="F6" s="12">
+        <v>84</v>
+      </c>
+      <c r="G6" s="12">
+        <v>82</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="9">
+        <v>110</v>
+      </c>
+      <c r="C7" s="10">
+        <v>70</v>
+      </c>
+      <c r="D7" s="10">
+        <v>156</v>
+      </c>
+      <c r="E7" s="10">
+        <v>64</v>
+      </c>
+      <c r="F7" s="10">
+        <v>84</v>
+      </c>
+      <c r="G7" s="10">
+        <v>89</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="11">
+        <v>140</v>
+      </c>
+      <c r="C8" s="12">
+        <v>90</v>
+      </c>
+      <c r="D8" s="12">
         <v>154</v>
       </c>
-      <c r="E3" s="2">
-        <v>66</v>
-      </c>
-      <c r="F3" s="2">
-        <v>95</v>
-      </c>
-      <c r="G3" s="2">
-        <v>87</v>
-      </c>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
-        <v>120</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="E8" s="12">
+        <v>67</v>
+      </c>
+      <c r="F8" s="12">
+        <v>80</v>
+      </c>
+      <c r="G8" s="12">
+        <v>75</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="11">
+        <v>110</v>
+      </c>
+      <c r="C9" s="12">
         <v>70</v>
       </c>
-      <c r="D4" s="4">
-        <v>170</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="D9" s="12">
+        <v>158</v>
+      </c>
+      <c r="E9" s="12">
+        <v>64</v>
+      </c>
+      <c r="F9" s="12">
+        <v>80</v>
+      </c>
+      <c r="G9" s="12">
         <v>84</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="11">
+        <v>110</v>
+      </c>
+      <c r="C10" s="12">
+        <v>70</v>
+      </c>
+      <c r="D10" s="12">
+        <v>158</v>
+      </c>
+      <c r="E10" s="12">
+        <v>61</v>
+      </c>
+      <c r="F10" s="12">
+        <v>84</v>
+      </c>
+      <c r="G10" s="12">
         <v>86</v>
       </c>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3">
-        <v>120</v>
-      </c>
-      <c r="C5" s="4">
-        <v>80</v>
-      </c>
-      <c r="D5" s="4">
-        <v>174</v>
-      </c>
-      <c r="E5" s="4">
-        <v>74</v>
-      </c>
-      <c r="F5" s="4">
-        <v>84</v>
-      </c>
-      <c r="G5" s="4">
-        <v>98</v>
-      </c>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="16"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="16"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="16"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="16"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="16"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="16"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2E7BC3B-EBAF-45C6-B79B-0DFBBBB18FEC}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>85770207572</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/datasehat.xlsx
+++ b/datasehat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\sehatselenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8CD937-6DE7-44CD-817A-2209422D71B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E0EDC7-1D0E-4DCA-8A4E-8BA82CB610AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8604" yWindow="1884" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
+    <workbookView xWindow="8604" yWindow="3360" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>nama</t>
   </si>
@@ -106,31 +106,13 @@
     <t>alamat</t>
   </si>
   <si>
-    <t>RONGGUR HALOMOAN LUBIS</t>
-  </si>
-  <si>
-    <t>NURYANDI</t>
-  </si>
-  <si>
-    <t>AHMAD BUKHORI</t>
-  </si>
-  <si>
-    <t>SYAM RAGIL RAHARJO</t>
-  </si>
-  <si>
-    <t>SURYA CAHYA DININGRAT</t>
-  </si>
-  <si>
-    <t>DIAN NOVITA SARI</t>
-  </si>
-  <si>
-    <t>USNIAWATI</t>
-  </si>
-  <si>
-    <t>RINI SUTARTI</t>
-  </si>
-  <si>
-    <t>ZIDNA RAHAYU</t>
+    <t>RIYAN ADRIAN WIBISONO</t>
+  </si>
+  <si>
+    <t>MAKSUDI</t>
+  </si>
+  <si>
+    <t>TIYA SETIYA</t>
   </si>
 </sst>
 </file>
@@ -184,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -276,11 +258,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -312,9 +305,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -323,6 +313,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,229 +680,145 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="19">
         <v>110</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="20">
         <v>70</v>
       </c>
-      <c r="D2" s="10">
-        <v>156</v>
-      </c>
-      <c r="E2" s="10">
-        <v>92</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="D2" s="20">
+        <v>160</v>
+      </c>
+      <c r="E2" s="20">
+        <v>62</v>
+      </c>
+      <c r="F2" s="20">
         <v>80</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="20">
         <v>82</v>
       </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11">
-        <v>130</v>
-      </c>
-      <c r="C3" s="12">
-        <v>90</v>
-      </c>
-      <c r="D3" s="12">
-        <v>156</v>
-      </c>
-      <c r="E3" s="12">
+      <c r="B3" s="21">
+        <v>120</v>
+      </c>
+      <c r="C3" s="22">
+        <v>80</v>
+      </c>
+      <c r="D3" s="22">
+        <v>160</v>
+      </c>
+      <c r="E3" s="22">
+        <v>60</v>
+      </c>
+      <c r="F3" s="22">
+        <v>84</v>
+      </c>
+      <c r="G3" s="22">
+        <v>84</v>
+      </c>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="21">
+        <v>110</v>
+      </c>
+      <c r="C4" s="22">
         <v>70</v>
       </c>
-      <c r="F3" s="12">
+      <c r="D4" s="22">
+        <v>158</v>
+      </c>
+      <c r="E4" s="22">
+        <v>56</v>
+      </c>
+      <c r="F4" s="22">
+        <v>80</v>
+      </c>
+      <c r="G4" s="22">
         <v>86</v>
       </c>
-      <c r="G3" s="12">
-        <v>82</v>
-      </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="11">
-        <v>100</v>
-      </c>
-      <c r="C4" s="12">
-        <v>70</v>
-      </c>
-      <c r="D4" s="12">
-        <v>158</v>
-      </c>
-      <c r="E4" s="12">
-        <v>55</v>
-      </c>
-      <c r="F4" s="12">
-        <v>86</v>
-      </c>
-      <c r="G4" s="12">
-        <v>83</v>
-      </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="11">
-        <v>100</v>
-      </c>
-      <c r="C5" s="12">
-        <v>60</v>
-      </c>
-      <c r="D5" s="12">
-        <v>157</v>
-      </c>
-      <c r="E5" s="12">
-        <v>81</v>
-      </c>
-      <c r="F5" s="12">
-        <v>82</v>
-      </c>
-      <c r="G5" s="12">
-        <v>84</v>
-      </c>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="11">
-        <v>120</v>
-      </c>
-      <c r="C6" s="12">
-        <v>80</v>
-      </c>
-      <c r="D6" s="12">
-        <v>156</v>
-      </c>
-      <c r="E6" s="12">
-        <v>58</v>
-      </c>
-      <c r="F6" s="12">
-        <v>84</v>
-      </c>
-      <c r="G6" s="12">
-        <v>82</v>
-      </c>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="9">
-        <v>110</v>
-      </c>
-      <c r="C7" s="10">
-        <v>70</v>
-      </c>
-      <c r="D7" s="10">
-        <v>156</v>
-      </c>
-      <c r="E7" s="10">
-        <v>64</v>
-      </c>
-      <c r="F7" s="10">
-        <v>84</v>
-      </c>
-      <c r="G7" s="10">
-        <v>89</v>
-      </c>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="11">
-        <v>140</v>
-      </c>
-      <c r="C8" s="12">
-        <v>90</v>
-      </c>
-      <c r="D8" s="12">
-        <v>154</v>
-      </c>
-      <c r="E8" s="12">
-        <v>67</v>
-      </c>
-      <c r="F8" s="12">
-        <v>80</v>
-      </c>
-      <c r="G8" s="12">
-        <v>75</v>
-      </c>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="11">
-        <v>110</v>
-      </c>
-      <c r="C9" s="12">
-        <v>70</v>
-      </c>
-      <c r="D9" s="12">
-        <v>158</v>
-      </c>
-      <c r="E9" s="12">
-        <v>64</v>
-      </c>
-      <c r="F9" s="12">
-        <v>80</v>
-      </c>
-      <c r="G9" s="12">
-        <v>84</v>
-      </c>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="11">
-        <v>110</v>
-      </c>
-      <c r="C10" s="12">
-        <v>70</v>
-      </c>
-      <c r="D10" s="12">
-        <v>158</v>
-      </c>
-      <c r="E10" s="12">
-        <v>61</v>
-      </c>
-      <c r="F10" s="12">
-        <v>84</v>
-      </c>
-      <c r="G10" s="12">
-        <v>86</v>
-      </c>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -905,33 +832,26 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -944,7 +864,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
@@ -952,44 +872,46 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-    </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
@@ -998,7 +920,7 @@
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12"/>
@@ -1007,7 +929,7 @@
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12"/>
@@ -1016,7 +938,7 @@
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12"/>
@@ -1025,7 +947,7 @@
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
@@ -1034,95 +956,95 @@
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-    </row>
-    <row r="30" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="16"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="16"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
     </row>
     <row r="34" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="16"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
     </row>
     <row r="35" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="16"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="16"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="1"/>

--- a/datasehat.xlsx
+++ b/datasehat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\sehatselenium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E0EDC7-1D0E-4DCA-8A4E-8BA82CB610AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E103D934-F274-478D-954B-B28CB9E73765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8604" yWindow="3360" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
+    <workbookView xWindow="8280" yWindow="2232" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>nama</t>
   </si>
@@ -106,13 +106,7 @@
     <t>alamat</t>
   </si>
   <si>
-    <t>RIYAN ADRIAN WIBISONO</t>
-  </si>
-  <si>
-    <t>MAKSUDI</t>
-  </si>
-  <si>
-    <t>TIYA SETIYA</t>
+    <t>SIGIT PRATAMA</t>
   </si>
 </sst>
 </file>
@@ -317,9 +311,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -334,6 +325,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -679,156 +673,107 @@
       </c>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="19">
-        <v>110</v>
-      </c>
-      <c r="C2" s="20">
-        <v>70</v>
-      </c>
-      <c r="D2" s="20">
+      <c r="B2" s="18">
+        <v>130</v>
+      </c>
+      <c r="C2" s="19">
+        <v>90</v>
+      </c>
+      <c r="D2" s="19">
         <v>160</v>
       </c>
-      <c r="E2" s="20">
-        <v>62</v>
-      </c>
-      <c r="F2" s="20">
-        <v>80</v>
-      </c>
-      <c r="G2" s="20">
+      <c r="E2" s="19">
+        <v>55</v>
+      </c>
+      <c r="F2" s="19">
         <v>82</v>
       </c>
+      <c r="G2" s="19">
+        <v>85</v>
+      </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="21">
-        <v>120</v>
-      </c>
-      <c r="C3" s="22">
-        <v>80</v>
-      </c>
-      <c r="D3" s="22">
-        <v>160</v>
-      </c>
-      <c r="E3" s="22">
-        <v>60</v>
-      </c>
-      <c r="F3" s="22">
-        <v>84</v>
-      </c>
-      <c r="G3" s="22">
-        <v>84</v>
-      </c>
+      <c r="A3" s="16"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="21">
-        <v>110</v>
-      </c>
-      <c r="C4" s="22">
-        <v>70</v>
-      </c>
-      <c r="D4" s="22">
-        <v>158</v>
-      </c>
-      <c r="E4" s="22">
-        <v>56</v>
-      </c>
-      <c r="F4" s="22">
-        <v>80</v>
-      </c>
-      <c r="G4" s="22">
-        <v>86</v>
-      </c>
+      <c r="A4" s="22"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -872,7 +817,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
-      <c r="H17" s="18"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11"/>
@@ -882,7 +827,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
-      <c r="H18" s="18"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>

--- a/datasehat.xlsx
+++ b/datasehat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\sehatselenium\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Pictures\bot-sehatindonesiaku\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E103D934-F274-478D-954B-B28CB9E73765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979E347D-2F32-4CCF-ACA0-6EE1655406F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="2232" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
+    <workbookView xWindow="8340" yWindow="2232" windowWidth="14436" windowHeight="8880" xr2:uid="{204D681D-D5A1-4808-BEE3-E0115C09E5E0}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>nama</t>
   </si>
@@ -106,14 +106,206 @@
     <t>alamat</t>
   </si>
   <si>
-    <t>SIGIT PRATAMA</t>
+    <t>MARDANI</t>
+  </si>
+  <si>
+    <t>KRISTIANI MARLINA BR PURBA</t>
+  </si>
+  <si>
+    <t>FIRDAUS</t>
+  </si>
+  <si>
+    <t>ARIAH</t>
+  </si>
+  <si>
+    <t>RATNA DWI JAYANTI</t>
+  </si>
+  <si>
+    <t>DARTO EVENSUS PAKPAHAN</t>
+  </si>
+  <si>
+    <t>NUR ASIYAH</t>
+  </si>
+  <si>
+    <t>CHRISTINA SIMAMORA</t>
+  </si>
+  <si>
+    <t>MUSI</t>
+  </si>
+  <si>
+    <t>ZORYA BATHARANDRA ICHSAN</t>
+  </si>
+  <si>
+    <t>BUNGA ACIPTA RIZKY</t>
+  </si>
+  <si>
+    <t>MUHAMAD JUL ANGGARA</t>
+  </si>
+  <si>
+    <t>PAKIATUL PULUNG</t>
+  </si>
+  <si>
+    <t>ROSIDAH</t>
+  </si>
+  <si>
+    <t>ARFAN SYAHPUTRA</t>
+  </si>
+  <si>
+    <t>BINUR PAKPAHAN</t>
+  </si>
+  <si>
+    <t>KHOPIPAH PAULA NISA</t>
+  </si>
+  <si>
+    <t>WARSENO</t>
+  </si>
+  <si>
+    <t>TINA</t>
+  </si>
+  <si>
+    <t>SUPRIYANTO</t>
+  </si>
+  <si>
+    <t>RAVI PERNAMA PUTRA</t>
+  </si>
+  <si>
+    <t>RONNY GURITNO</t>
+  </si>
+  <si>
+    <t>RUSNAWATI</t>
+  </si>
+  <si>
+    <t>ILHAM MAULANA</t>
+  </si>
+  <si>
+    <t>MUHAYA</t>
+  </si>
+  <si>
+    <t>MIRNA NAINGGOLAN</t>
+  </si>
+  <si>
+    <t>NENI YULIANI</t>
+  </si>
+  <si>
+    <t>KARSID</t>
+  </si>
+  <si>
+    <t>DEASY RATNASARI</t>
+  </si>
+  <si>
+    <t>M SOLEH</t>
+  </si>
+  <si>
+    <t>OJAH</t>
+  </si>
+  <si>
+    <t>M I A</t>
+  </si>
+  <si>
+    <t>LAILATUL QOMARIAH</t>
+  </si>
+  <si>
+    <t>YOSANA</t>
+  </si>
+  <si>
+    <t>ADE</t>
+  </si>
+  <si>
+    <t>RUDI NUGRAHA</t>
+  </si>
+  <si>
+    <t>EKA JULAEKA</t>
+  </si>
+  <si>
+    <t>MARIO FITRIYADI</t>
+  </si>
+  <si>
+    <t>RINI</t>
+  </si>
+  <si>
+    <t>SADAM HUSEIN</t>
+  </si>
+  <si>
+    <t>ALAN ADITIA</t>
+  </si>
+  <si>
+    <t>JONATHAN WILLIAM F</t>
+  </si>
+  <si>
+    <t>TAN CUISEN</t>
+  </si>
+  <si>
+    <t>NIKSON TUHEHAY</t>
+  </si>
+  <si>
+    <t>M. MANE MOGEN</t>
+  </si>
+  <si>
+    <t>JUZIRRA MANUHUTU</t>
+  </si>
+  <si>
+    <t>AGUS SETIAWAN</t>
+  </si>
+  <si>
+    <t>SANTOSO</t>
+  </si>
+  <si>
+    <t>NISRAMAH ZEBUA</t>
+  </si>
+  <si>
+    <t>SUSANTO</t>
+  </si>
+  <si>
+    <t>HENDRA SITORUS</t>
+  </si>
+  <si>
+    <t>URBANUS DJABUMONA</t>
+  </si>
+  <si>
+    <t>AHMAD ROPII ABDILAH</t>
+  </si>
+  <si>
+    <t>EMILITA SEPTIANI</t>
+  </si>
+  <si>
+    <t>ISYANTO</t>
+  </si>
+  <si>
+    <t>SUPI ARDIYANTO</t>
+  </si>
+  <si>
+    <t>JOSE ALLEXANDRO KEBAOWOLO</t>
+  </si>
+  <si>
+    <t>SRI KURNIASIH</t>
+  </si>
+  <si>
+    <t>DIRAH</t>
+  </si>
+  <si>
+    <t>INGGIL RISKY NINGTIYAS</t>
+  </si>
+  <si>
+    <t>TITIN SUMARTINI</t>
+  </si>
+  <si>
+    <t>AZARYA JUNIOR PARLINGGOMAN RAJA GUKGUK</t>
+  </si>
+  <si>
+    <t>SELAMET WIJAYA</t>
+  </si>
+  <si>
+    <t>YUSTI</t>
+  </si>
+  <si>
+    <t>LISTIAWATI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,14 +320,26 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="8"/>
+      <color rgb="FF343A40"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF343A40"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -160,7 +364,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -263,71 +467,79 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,361 +855,1548 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE509DE-262C-4991-9047-33EC594D87BB}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="12">
+        <v>148</v>
+      </c>
+      <c r="C2" s="13">
+        <v>80</v>
+      </c>
+      <c r="D2" s="12">
+        <v>166</v>
+      </c>
+      <c r="E2" s="13">
+        <v>50</v>
+      </c>
+      <c r="F2" s="13">
+        <v>72</v>
+      </c>
+      <c r="G2" s="9">
+        <v>84</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="25.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="15">
+        <v>111</v>
+      </c>
+      <c r="C3" s="16">
+        <v>69</v>
+      </c>
+      <c r="D3" s="15">
+        <v>156</v>
+      </c>
+      <c r="E3" s="16">
+        <v>53</v>
+      </c>
+      <c r="F3" s="16">
+        <v>84</v>
+      </c>
+      <c r="G3" s="7">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="15">
+        <v>125</v>
+      </c>
+      <c r="C4" s="16">
+        <v>88</v>
+      </c>
+      <c r="D4" s="15">
+        <v>168</v>
+      </c>
+      <c r="E4" s="16">
+        <v>64</v>
+      </c>
+      <c r="F4" s="16">
+        <v>82</v>
+      </c>
+      <c r="G4" s="7">
+        <v>96</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="15">
+        <v>152</v>
+      </c>
+      <c r="C5" s="16">
+        <v>81</v>
+      </c>
+      <c r="D5" s="15">
+        <v>144</v>
+      </c>
+      <c r="E5" s="16">
+        <v>57</v>
+      </c>
+      <c r="F5" s="16">
+        <v>67</v>
+      </c>
+      <c r="G5" s="7">
+        <v>87</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="15">
+        <v>110</v>
+      </c>
+      <c r="C6" s="16">
+        <v>70</v>
+      </c>
+      <c r="D6" s="15">
+        <v>155</v>
+      </c>
+      <c r="E6" s="17">
+        <v>46.7</v>
+      </c>
+      <c r="F6" s="16">
+        <v>80</v>
+      </c>
+      <c r="G6" s="7">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="15">
+        <v>120</v>
+      </c>
+      <c r="C7" s="16">
+        <v>80</v>
+      </c>
+      <c r="D7" s="15">
+        <v>165</v>
+      </c>
+      <c r="E7" s="16">
+        <v>70</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="7">
+        <v>96</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="15">
+        <v>160</v>
+      </c>
+      <c r="C8" s="16">
+        <v>85</v>
+      </c>
+      <c r="D8" s="15">
+        <v>154</v>
+      </c>
+      <c r="E8" s="16">
+        <v>68</v>
+      </c>
+      <c r="F8" s="16">
+        <v>98</v>
+      </c>
+      <c r="G8" s="14">
+        <v>121</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="15">
+        <v>120</v>
+      </c>
+      <c r="C9" s="16">
+        <v>80</v>
+      </c>
+      <c r="D9" s="15">
+        <v>165</v>
+      </c>
+      <c r="E9" s="16">
+        <v>99</v>
+      </c>
+      <c r="F9" s="16">
+        <v>80</v>
+      </c>
+      <c r="G9" s="14">
+        <v>111</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="15">
+        <v>120</v>
+      </c>
+      <c r="C10" s="16">
+        <v>80</v>
+      </c>
+      <c r="D10" s="15">
+        <v>155</v>
+      </c>
+      <c r="E10" s="16">
+        <v>55</v>
+      </c>
+      <c r="F10" s="16">
+        <v>60</v>
+      </c>
+      <c r="G10" s="7">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" ht="25.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="15">
+        <v>115</v>
+      </c>
+      <c r="C11" s="16">
+        <v>64</v>
+      </c>
+      <c r="D11" s="15">
+        <v>171</v>
+      </c>
+      <c r="E11" s="16">
+        <v>78</v>
+      </c>
+      <c r="F11" s="16">
+        <v>84</v>
+      </c>
+      <c r="G11" s="7">
+        <v>87</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="15">
+        <v>131</v>
+      </c>
+      <c r="C12" s="16">
+        <v>91</v>
+      </c>
+      <c r="D12" s="15">
+        <v>159</v>
+      </c>
+      <c r="E12" s="17">
+        <v>73.8</v>
+      </c>
+      <c r="F12" s="16">
+        <v>70</v>
+      </c>
+      <c r="G12" s="9">
+        <v>84</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="15">
+        <v>102</v>
+      </c>
+      <c r="C13" s="16">
+        <v>71</v>
+      </c>
+      <c r="D13" s="15">
+        <v>166</v>
+      </c>
+      <c r="E13" s="16">
+        <v>47</v>
+      </c>
+      <c r="F13" s="16">
+        <v>70</v>
+      </c>
+      <c r="G13" s="7">
+        <v>96</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="15">
+        <v>98</v>
+      </c>
+      <c r="C14" s="16">
+        <v>65</v>
+      </c>
+      <c r="D14" s="15">
+        <v>162</v>
+      </c>
+      <c r="E14" s="16">
+        <v>38</v>
+      </c>
+      <c r="F14" s="16">
+        <v>68</v>
+      </c>
+      <c r="G14" s="7">
+        <v>132</v>
+      </c>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="15">
+        <v>160</v>
+      </c>
+      <c r="C15" s="16">
+        <v>83</v>
+      </c>
+      <c r="D15" s="15">
+        <v>153</v>
+      </c>
+      <c r="E15" s="16">
+        <v>78</v>
+      </c>
+      <c r="F15" s="16">
+        <v>102</v>
+      </c>
+      <c r="G15" s="9">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="12">
+        <v>98</v>
+      </c>
+      <c r="C16" s="13">
+        <v>79</v>
+      </c>
+      <c r="D16" s="12">
+        <v>30</v>
+      </c>
+      <c r="E16" s="13">
+        <v>30</v>
+      </c>
+      <c r="F16" s="13">
+        <v>70</v>
+      </c>
+      <c r="G16" s="9">
+        <v>84</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="15">
+        <v>120</v>
+      </c>
+      <c r="C17" s="16">
+        <v>70</v>
+      </c>
+      <c r="D17" s="15">
+        <v>155</v>
+      </c>
+      <c r="E17" s="16">
+        <v>60</v>
+      </c>
+      <c r="F17" s="16">
+        <v>70</v>
+      </c>
+      <c r="G17" s="7">
+        <v>100</v>
+      </c>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="15">
+        <v>116</v>
+      </c>
+      <c r="C18" s="16">
+        <v>70</v>
+      </c>
+      <c r="D18" s="15">
+        <v>160</v>
+      </c>
+      <c r="E18" s="16">
+        <v>59</v>
+      </c>
+      <c r="F18" s="16">
+        <v>83</v>
+      </c>
+      <c r="G18" s="7">
+        <v>96</v>
+      </c>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="15">
+        <v>135</v>
+      </c>
+      <c r="C19" s="16">
+        <v>86</v>
+      </c>
+      <c r="D19" s="15">
+        <v>178</v>
+      </c>
+      <c r="E19" s="16">
+        <v>93</v>
+      </c>
+      <c r="F19" s="16">
+        <v>87</v>
+      </c>
+      <c r="G19" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="15">
+        <v>133</v>
+      </c>
+      <c r="C20" s="16">
+        <v>92</v>
+      </c>
+      <c r="D20" s="15">
+        <v>157</v>
+      </c>
+      <c r="E20" s="16">
+        <v>58</v>
+      </c>
+      <c r="F20" s="16">
+        <v>82</v>
+      </c>
+      <c r="G20" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="15">
+        <v>143</v>
+      </c>
+      <c r="C21" s="16">
+        <v>78</v>
+      </c>
+      <c r="D21" s="15">
+        <v>165</v>
+      </c>
+      <c r="E21" s="16">
+        <v>55</v>
+      </c>
+      <c r="F21" s="16">
+        <v>67</v>
+      </c>
+      <c r="G21" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="15">
+        <v>90</v>
+      </c>
+      <c r="C22" s="16">
+        <v>60</v>
+      </c>
+      <c r="D22" s="15">
+        <v>167</v>
+      </c>
+      <c r="E22" s="17">
+        <v>61.2</v>
+      </c>
+      <c r="F22" s="16">
+        <v>70</v>
+      </c>
+      <c r="G22" s="14">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="15">
+        <v>143</v>
+      </c>
+      <c r="C23" s="16">
+        <v>86</v>
+      </c>
+      <c r="D23" s="15">
+        <v>170</v>
+      </c>
+      <c r="E23" s="16">
+        <v>58</v>
+      </c>
+      <c r="F23" s="16">
+        <v>70</v>
+      </c>
+      <c r="G23" s="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="15">
+        <v>101</v>
+      </c>
+      <c r="C24" s="16">
+        <v>54</v>
+      </c>
+      <c r="D24" s="15">
+        <v>150</v>
+      </c>
+      <c r="E24" s="16">
+        <v>38</v>
+      </c>
+      <c r="F24" s="16">
+        <v>77</v>
+      </c>
+      <c r="G24" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="15">
+        <v>117</v>
+      </c>
+      <c r="C25" s="16">
+        <v>78</v>
+      </c>
+      <c r="D25" s="15">
+        <v>170</v>
+      </c>
+      <c r="E25" s="16">
+        <v>50</v>
+      </c>
+      <c r="F25" s="16">
+        <v>65</v>
+      </c>
+      <c r="G25" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="15">
+        <v>146</v>
+      </c>
+      <c r="C26" s="16">
+        <v>77</v>
+      </c>
+      <c r="D26" s="15">
+        <v>150</v>
+      </c>
+      <c r="E26" s="16">
+        <v>50</v>
+      </c>
+      <c r="F26" s="16">
+        <v>85</v>
+      </c>
+      <c r="G26" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="15">
         <v>130</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C27" s="16">
+        <v>80</v>
+      </c>
+      <c r="D27" s="15">
+        <v>150</v>
+      </c>
+      <c r="E27" s="16">
+        <v>65</v>
+      </c>
+      <c r="F27" s="16">
+        <v>70</v>
+      </c>
+      <c r="G27" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="15">
+        <v>130</v>
+      </c>
+      <c r="C28" s="16">
+        <v>80</v>
+      </c>
+      <c r="D28" s="15">
+        <v>155</v>
+      </c>
+      <c r="E28" s="16">
+        <v>65</v>
+      </c>
+      <c r="F28" s="16">
+        <v>85</v>
+      </c>
+      <c r="G28" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="12">
+        <v>141</v>
+      </c>
+      <c r="C29" s="13">
+        <v>82</v>
+      </c>
+      <c r="D29" s="10">
+        <v>158.9</v>
+      </c>
+      <c r="E29" s="13">
+        <v>61</v>
+      </c>
+      <c r="F29" s="13">
+        <v>87</v>
+      </c>
+      <c r="G29" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="15">
+        <v>120</v>
+      </c>
+      <c r="C30" s="16">
+        <v>80</v>
+      </c>
+      <c r="D30" s="15">
+        <v>160</v>
+      </c>
+      <c r="E30" s="16">
+        <v>70</v>
+      </c>
+      <c r="F30" s="16">
+        <v>70</v>
+      </c>
+      <c r="G30" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="15">
+        <v>116</v>
+      </c>
+      <c r="C31" s="16">
+        <v>68</v>
+      </c>
+      <c r="D31" s="15">
+        <v>171</v>
+      </c>
+      <c r="E31" s="16">
+        <v>83</v>
+      </c>
+      <c r="F31" s="16">
+        <v>80</v>
+      </c>
+      <c r="G31" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="15">
+        <v>156</v>
+      </c>
+      <c r="C32" s="16">
+        <v>86</v>
+      </c>
+      <c r="D32" s="15">
+        <v>155</v>
+      </c>
+      <c r="E32" s="16">
+        <v>55</v>
+      </c>
+      <c r="F32" s="16">
+        <v>65</v>
+      </c>
+      <c r="G32" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="15">
+        <v>107</v>
+      </c>
+      <c r="C33" s="16">
+        <v>77</v>
+      </c>
+      <c r="D33" s="15">
+        <v>151</v>
+      </c>
+      <c r="E33" s="16">
+        <v>59</v>
+      </c>
+      <c r="F33" s="16">
+        <v>87</v>
+      </c>
+      <c r="G33" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="15">
+        <v>124</v>
+      </c>
+      <c r="C34" s="16">
+        <v>77</v>
+      </c>
+      <c r="D34" s="15">
+        <v>160</v>
+      </c>
+      <c r="E34" s="16">
+        <v>85</v>
+      </c>
+      <c r="F34" s="16">
+        <v>82</v>
+      </c>
+      <c r="G34" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="15">
+        <v>162</v>
+      </c>
+      <c r="C35" s="16">
+        <v>106</v>
+      </c>
+      <c r="D35" s="15">
+        <v>155</v>
+      </c>
+      <c r="E35" s="16">
+        <v>73</v>
+      </c>
+      <c r="F35" s="16">
+        <v>84</v>
+      </c>
+      <c r="G35" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="15">
+        <v>180</v>
+      </c>
+      <c r="C36" s="16">
+        <v>100</v>
+      </c>
+      <c r="D36" s="15">
+        <v>160</v>
+      </c>
+      <c r="E36" s="16">
+        <v>60</v>
+      </c>
+      <c r="F36" s="16">
+        <v>70</v>
+      </c>
+      <c r="G36" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="15">
+        <v>120</v>
+      </c>
+      <c r="C37" s="16">
+        <v>80</v>
+      </c>
+      <c r="D37" s="15">
+        <v>175</v>
+      </c>
+      <c r="E37" s="16">
+        <v>61</v>
+      </c>
+      <c r="F37" s="16">
+        <v>88</v>
+      </c>
+      <c r="G37" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="15">
+        <v>130</v>
+      </c>
+      <c r="C38" s="16">
+        <v>80</v>
+      </c>
+      <c r="D38" s="15">
+        <v>150</v>
+      </c>
+      <c r="E38" s="16">
+        <v>63</v>
+      </c>
+      <c r="F38" s="16">
+        <v>70</v>
+      </c>
+      <c r="G38" s="14">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="15">
+        <v>120</v>
+      </c>
+      <c r="C39" s="16">
+        <v>88</v>
+      </c>
+      <c r="D39" s="15">
+        <v>177</v>
+      </c>
+      <c r="E39" s="16">
+        <v>95</v>
+      </c>
+      <c r="F39" s="16">
+        <v>150</v>
+      </c>
+      <c r="G39" s="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="15">
+        <v>156</v>
+      </c>
+      <c r="C40" s="16">
+        <v>93</v>
+      </c>
+      <c r="D40" s="15">
+        <v>150</v>
+      </c>
+      <c r="E40" s="16">
+        <v>54</v>
+      </c>
+      <c r="F40" s="16">
+        <v>80</v>
+      </c>
+      <c r="G40" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="15">
+        <v>130</v>
+      </c>
+      <c r="C41" s="16">
+        <v>80</v>
+      </c>
+      <c r="D41" s="15">
+        <v>155</v>
+      </c>
+      <c r="E41" s="16">
+        <v>65</v>
+      </c>
+      <c r="F41" s="16">
+        <v>85</v>
+      </c>
+      <c r="G41" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="12">
+        <v>141</v>
+      </c>
+      <c r="C42" s="13">
+        <v>82</v>
+      </c>
+      <c r="D42" s="10">
+        <v>158.9</v>
+      </c>
+      <c r="E42" s="13">
+        <v>61</v>
+      </c>
+      <c r="F42" s="13">
+        <v>87</v>
+      </c>
+      <c r="G42" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="15">
+        <v>120</v>
+      </c>
+      <c r="C43" s="16">
+        <v>80</v>
+      </c>
+      <c r="D43" s="15">
+        <v>160</v>
+      </c>
+      <c r="E43" s="16">
+        <v>70</v>
+      </c>
+      <c r="F43" s="16">
+        <v>70</v>
+      </c>
+      <c r="G43" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="15">
+        <v>116</v>
+      </c>
+      <c r="C44" s="16">
+        <v>68</v>
+      </c>
+      <c r="D44" s="15">
+        <v>171</v>
+      </c>
+      <c r="E44" s="16">
+        <v>83</v>
+      </c>
+      <c r="F44" s="16">
+        <v>80</v>
+      </c>
+      <c r="G44" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="15">
+        <v>156</v>
+      </c>
+      <c r="C45" s="16">
+        <v>86</v>
+      </c>
+      <c r="D45" s="15">
+        <v>155</v>
+      </c>
+      <c r="E45" s="16">
+        <v>55</v>
+      </c>
+      <c r="F45" s="16">
+        <v>65</v>
+      </c>
+      <c r="G45" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="15">
+        <v>107</v>
+      </c>
+      <c r="C46" s="16">
+        <v>77</v>
+      </c>
+      <c r="D46" s="15">
+        <v>151</v>
+      </c>
+      <c r="E46" s="16">
+        <v>59</v>
+      </c>
+      <c r="F46" s="16">
+        <v>87</v>
+      </c>
+      <c r="G46" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="15">
+        <v>124</v>
+      </c>
+      <c r="C47" s="16">
+        <v>77</v>
+      </c>
+      <c r="D47" s="15">
+        <v>160</v>
+      </c>
+      <c r="E47" s="16">
+        <v>85</v>
+      </c>
+      <c r="F47" s="16">
+        <v>82</v>
+      </c>
+      <c r="G47" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="15">
+        <v>162</v>
+      </c>
+      <c r="C48" s="16">
+        <v>106</v>
+      </c>
+      <c r="D48" s="15">
+        <v>155</v>
+      </c>
+      <c r="E48" s="16">
+        <v>73</v>
+      </c>
+      <c r="F48" s="16">
+        <v>84</v>
+      </c>
+      <c r="G48" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="15">
+        <v>180</v>
+      </c>
+      <c r="C49" s="16">
+        <v>100</v>
+      </c>
+      <c r="D49" s="15">
+        <v>160</v>
+      </c>
+      <c r="E49" s="16">
+        <v>60</v>
+      </c>
+      <c r="F49" s="16">
+        <v>70</v>
+      </c>
+      <c r="G49" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="15">
+        <v>120</v>
+      </c>
+      <c r="C50" s="16">
+        <v>80</v>
+      </c>
+      <c r="D50" s="15">
+        <v>175</v>
+      </c>
+      <c r="E50" s="16">
+        <v>61</v>
+      </c>
+      <c r="F50" s="16">
+        <v>88</v>
+      </c>
+      <c r="G50" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="15">
+        <v>130</v>
+      </c>
+      <c r="C51" s="16">
+        <v>80</v>
+      </c>
+      <c r="D51" s="15">
+        <v>150</v>
+      </c>
+      <c r="E51" s="16">
+        <v>63</v>
+      </c>
+      <c r="F51" s="16">
+        <v>70</v>
+      </c>
+      <c r="G51" s="14">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="15">
+        <v>120</v>
+      </c>
+      <c r="C52" s="16">
+        <v>88</v>
+      </c>
+      <c r="D52" s="15">
+        <v>177</v>
+      </c>
+      <c r="E52" s="16">
+        <v>95</v>
+      </c>
+      <c r="F52" s="16">
+        <v>150</v>
+      </c>
+      <c r="G52" s="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="15">
+        <v>156</v>
+      </c>
+      <c r="C53" s="16">
+        <v>93</v>
+      </c>
+      <c r="D53" s="15">
+        <v>150</v>
+      </c>
+      <c r="E53" s="16">
+        <v>54</v>
+      </c>
+      <c r="F53" s="16">
+        <v>80</v>
+      </c>
+      <c r="G53" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="12">
+        <v>122</v>
+      </c>
+      <c r="C54" s="13">
+        <v>89</v>
+      </c>
+      <c r="D54" s="12">
+        <v>165</v>
+      </c>
+      <c r="E54" s="13">
+        <v>56</v>
+      </c>
+      <c r="F54" s="13">
+        <v>78</v>
+      </c>
+      <c r="G54" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="15">
+        <v>120</v>
+      </c>
+      <c r="C55" s="16">
+        <v>83</v>
+      </c>
+      <c r="D55" s="15">
+        <v>165</v>
+      </c>
+      <c r="E55" s="16">
+        <v>66</v>
+      </c>
+      <c r="F55" s="16">
+        <v>78</v>
+      </c>
+      <c r="G55" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="15">
+        <v>120</v>
+      </c>
+      <c r="C56" s="16">
+        <v>80</v>
+      </c>
+      <c r="D56" s="15">
+        <v>155</v>
+      </c>
+      <c r="E56" s="16">
+        <v>58</v>
+      </c>
+      <c r="F56" s="21">
+        <v>80</v>
+      </c>
+      <c r="G56" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="15">
+        <v>160</v>
+      </c>
+      <c r="C57" s="16">
+        <v>100</v>
+      </c>
+      <c r="D57" s="15">
+        <v>160</v>
+      </c>
+      <c r="E57" s="16">
+        <v>80</v>
+      </c>
+      <c r="F57" s="16">
+        <v>98</v>
+      </c>
+      <c r="G57" s="7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="25.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="15">
+        <v>117</v>
+      </c>
+      <c r="C58" s="16">
+        <v>68</v>
+      </c>
+      <c r="D58" s="15">
+        <v>169</v>
+      </c>
+      <c r="E58" s="16">
+        <v>64</v>
+      </c>
+      <c r="F58" s="16">
+        <v>78</v>
+      </c>
+      <c r="G58" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" s="15">
+        <v>106</v>
+      </c>
+      <c r="C59" s="16">
+        <v>65</v>
+      </c>
+      <c r="D59" s="15">
+        <v>150</v>
+      </c>
+      <c r="E59" s="16">
+        <v>60</v>
+      </c>
+      <c r="F59" s="16">
+        <v>67</v>
+      </c>
+      <c r="G59" s="9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" s="15">
+        <v>150</v>
+      </c>
+      <c r="C60" s="16">
+        <v>94</v>
+      </c>
+      <c r="D60" s="15">
+        <v>150</v>
+      </c>
+      <c r="E60" s="16">
+        <v>60</v>
+      </c>
+      <c r="F60" s="16">
+        <v>67</v>
+      </c>
+      <c r="G60" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" s="15">
+        <v>116</v>
+      </c>
+      <c r="C61" s="16">
+        <v>70</v>
+      </c>
+      <c r="D61" s="15">
+        <v>157</v>
+      </c>
+      <c r="E61" s="16">
+        <v>54</v>
+      </c>
+      <c r="F61" s="16">
+        <v>67</v>
+      </c>
+      <c r="G61" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B62" s="15">
+        <v>131</v>
+      </c>
+      <c r="C62" s="16">
+        <v>92</v>
+      </c>
+      <c r="D62" s="15">
+        <v>150</v>
+      </c>
+      <c r="E62" s="16">
+        <v>36</v>
+      </c>
+      <c r="F62" s="16">
+        <v>78</v>
+      </c>
+      <c r="G62" s="7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="37.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="15">
+        <v>132</v>
+      </c>
+      <c r="C63" s="16">
+        <v>81</v>
+      </c>
+      <c r="D63" s="15">
+        <v>167</v>
+      </c>
+      <c r="E63" s="16">
+        <v>65</v>
+      </c>
+      <c r="F63" s="16">
+        <v>78</v>
+      </c>
+      <c r="G63" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="15">
+        <v>133</v>
+      </c>
+      <c r="C64" s="16">
+        <v>81</v>
+      </c>
+      <c r="D64" s="15">
+        <v>158</v>
+      </c>
+      <c r="E64" s="16">
+        <v>52</v>
+      </c>
+      <c r="F64" s="16">
+        <v>65</v>
+      </c>
+      <c r="G64" s="7">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="15">
+        <v>136</v>
+      </c>
+      <c r="C65" s="16">
+        <v>78</v>
+      </c>
+      <c r="D65" s="15">
+        <v>150</v>
+      </c>
+      <c r="E65" s="16">
+        <v>65</v>
+      </c>
+      <c r="F65" s="16">
+        <v>78</v>
+      </c>
+      <c r="G65" s="14">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="19">
-        <v>160</v>
-      </c>
-      <c r="E2" s="19">
-        <v>55</v>
-      </c>
-      <c r="F2" s="19">
-        <v>82</v>
-      </c>
-      <c r="G2" s="19">
-        <v>85</v>
-      </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="22"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="15"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="15"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="15"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="15"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-    </row>
-    <row r="33" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="15"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-    </row>
-    <row r="34" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="15"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-    </row>
-    <row r="35" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="15"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="15"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="1"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
+      <c r="B66" s="15">
+        <v>135</v>
+      </c>
+      <c r="C66" s="16">
+        <v>83</v>
+      </c>
+      <c r="D66" s="15">
+        <v>155</v>
+      </c>
+      <c r="E66" s="16">
+        <v>57</v>
+      </c>
+      <c r="F66" s="16">
+        <v>78</v>
+      </c>
+      <c r="G66" s="14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G67" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1058,13 +2457,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D2" t="s">
